--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487084_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487084_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.0936</v>
+        <v>3.699</v>
       </c>
       <c r="E2" t="n">
-        <v>5.2095</v>
+        <v>4.8685</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.1159</v>
+        <v>-1.1695</v>
       </c>
       <c r="G2" t="n">
         <v>1.6156</v>
@@ -610,13 +610,13 @@
         <v>1.3511</v>
       </c>
       <c r="S2" t="n">
-        <v>1.478</v>
+        <v>1.0834</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8884</v>
+        <v>0.5473</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5896</v>
+        <v>0.536</v>
       </c>
       <c r="V2" t="n">
         <v>0.614</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.764</v>
+        <v>1.5905</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1325</v>
+        <v>1.9322</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3684</v>
+        <v>-0.3417</v>
       </c>
       <c r="G3" t="n">
         <v>0.5764</v>
@@ -688,13 +688,13 @@
         <v>1.158</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2095</v>
+        <v>0.036</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0278</v>
+        <v>-0.1725</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1818</v>
+        <v>0.2085</v>
       </c>
       <c r="V3" t="n">
         <v>-0.18</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6808</v>
+        <v>-0.1817</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4813</v>
+        <v>1.1809</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.8004</v>
+        <v>-1.3626</v>
       </c>
       <c r="G4" t="n">
         <v>0.3333</v>
@@ -766,13 +766,13 @@
         <v>0.579</v>
       </c>
       <c r="S4" t="n">
-        <v>1.8541</v>
+        <v>0.9915</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2803</v>
+        <v>-0.0201</v>
       </c>
       <c r="U4" t="n">
-        <v>1.5738</v>
+        <v>1.0116</v>
       </c>
       <c r="V4" t="n">
         <v>-2.0856</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. GUTIERREZ O´CALLAGHAN</t>
+          <t>L. BARNES HERNANDEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4893</v>
+        <v>-1.3981</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3306</v>
+        <v>-0.2678</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.8199</v>
+        <v>-1.1303</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.4346</v>
+        <v>-1.8943</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.6891</v>
+        <v>-1.2367</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7454</v>
+        <v>-0.6576</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5625</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4811</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0814</v>
+        <v>0.1628</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.9971</v>
+        <v>-1.9691</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.1702</v>
+        <v>-1.1487</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8268</v>
+        <v>-0.8204</v>
       </c>
       <c r="P5" t="n">
         <v>1.158</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1231</v>
+        <v>1.158</v>
       </c>
       <c r="S5" t="n">
-        <v>2.1952</v>
+        <v>0.8943</v>
       </c>
       <c r="T5" t="n">
-        <v>1.7332</v>
+        <v>0.3137</v>
       </c>
       <c r="U5" t="n">
-        <v>0.462</v>
+        <v>0.5807</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.4079</v>
+        <v>-1.5561</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.6562</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.4079</v>
+        <v>-0.8999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. BARNES HERNANDEZ</t>
+          <t>E. GUTIERREZ O´CALLAGHAN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.8706</v>
+        <v>-1.6652</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2329</v>
+        <v>0.2885</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.1035</v>
+        <v>-1.9538</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.8943</v>
+        <v>-2.4346</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.2367</v>
+        <v>-1.6891</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6576</v>
+        <v>-0.7454</v>
       </c>
       <c r="J6" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.5625</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.08799999999999999</v>
+        <v>0.4811</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1628</v>
+        <v>0.0814</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.9691</v>
+        <v>-2.9971</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.1487</v>
+        <v>-2.1702</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8204</v>
+        <v>-0.8268</v>
       </c>
       <c r="P6" t="n">
         <v>1.158</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R6" t="n">
-        <v>1.158</v>
+        <v>2.1231</v>
       </c>
       <c r="S6" t="n">
-        <v>1.4218</v>
+        <v>1.0193</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8144</v>
+        <v>0.6911</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6074000000000001</v>
+        <v>0.3282</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.5561</v>
+        <v>-1.4079</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.6562</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.8999</v>
+        <v>-1.4079</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.52</v>
+        <v>-1.706</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9136</v>
+        <v>1.674</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.4335</v>
+        <v>-3.38</v>
       </c>
       <c r="G7" t="n">
         <v>0.1439</v>
@@ -1000,13 +1000,13 @@
         <v>0.965</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1428</v>
+        <v>0.6712</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3424</v>
+        <v>0.4181</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1996</v>
+        <v>0.2531</v>
       </c>
       <c r="V7" t="n">
         <v>-1.5561</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. HANSEN GUTIERREZ</t>
+          <t>J. RODRIGUEZ NERI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.7981</v>
+        <v>-2.7131</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.613</v>
+        <v>-2.2289</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.1851</v>
+        <v>-0.4842</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.1754</v>
+        <v>1.0264</v>
       </c>
       <c r="H8" t="n">
-        <v>2.8938</v>
+        <v>0.4502</v>
       </c>
       <c r="I8" t="n">
-        <v>-4.0692</v>
+        <v>0.5762</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7203000000000001</v>
+        <v>2.6614</v>
       </c>
       <c r="K8" t="n">
-        <v>3.969</v>
+        <v>1.3919</v>
       </c>
       <c r="L8" t="n">
-        <v>-3.2488</v>
+        <v>1.2695</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.8956</v>
+        <v>-1.635</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.0752</v>
+        <v>-0.9417</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8204</v>
+        <v>-0.6933</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.579</v>
+        <v>-3.4741</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9301</v>
+        <v>-4.8252</v>
       </c>
       <c r="R8" t="n">
         <v>1.3511</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3642</v>
+        <v>0.6345</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0172</v>
+        <v>-0.06510000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3814</v>
+        <v>0.6996</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.4079</v>
+        <v>-0.8999</v>
       </c>
       <c r="W8" t="n">
-        <v>0.614</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.0219</v>
+        <v>-0.8999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. HERNANDEZ BLANCO</t>
+          <t>I. HANSEN GUTIERREZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.1315</v>
+        <v>-2.818</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2044</v>
+        <v>-0.7131</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9271</v>
+        <v>-2.1048</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.0422</v>
+        <v>-1.1754</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.0422</v>
+        <v>2.8938</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>-4.0692</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.9419</v>
+        <v>0.7203000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.2743</v>
+        <v>3.969</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6676</v>
+        <v>-3.2488</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1003</v>
+        <v>-1.8956</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7679</v>
+        <v>-1.0752</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6676</v>
+        <v>-0.8204</v>
       </c>
       <c r="P9" t="n">
         <v>-0.579</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R9" t="n">
-        <v>0.386</v>
+        <v>1.3511</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2822</v>
+        <v>0.3444</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2974</v>
+        <v>-0.1173</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0152</v>
+        <v>0.4617</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.228</v>
+        <v>-1.4079</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.614</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.228</v>
+        <v>-2.0219</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ NERI</t>
+          <t>P. HERNANDEZ BLANCO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.4607</v>
+        <v>-2.8975</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.7891</v>
+        <v>-2.1043</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6716</v>
+        <v>-0.7932</v>
       </c>
       <c r="G10" t="n">
-        <v>1.0264</v>
+        <v>-1.0422</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4502</v>
+        <v>-1.0422</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5762</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>2.6614</v>
+        <v>-0.9419</v>
       </c>
       <c r="K10" t="n">
-        <v>1.3919</v>
+        <v>-0.2743</v>
       </c>
       <c r="L10" t="n">
-        <v>1.2695</v>
+        <v>-0.6676</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.635</v>
+        <v>-0.1003</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.9417</v>
+        <v>-0.7679</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6933</v>
+        <v>0.6676</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.4741</v>
+        <v>-0.579</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.8252</v>
+        <v>-0.965</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3511</v>
+        <v>0.386</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.113</v>
+        <v>-0.0483</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6253</v>
+        <v>-0.1973</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5122</v>
+        <v>0.149</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.8999</v>
+        <v>-1.228</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.8999</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. SAEZ PEREZ</t>
+          <t>R. SANCHEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7668</v>
+        <v>-3.4547</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.4049</v>
+        <v>-0.5775</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.3619</v>
+        <v>-2.8772</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.1785</v>
+        <v>-2.5243</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4088</v>
+        <v>-1.1498</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.5873</v>
+        <v>-1.3745</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7702</v>
+        <v>0.3859</v>
       </c>
       <c r="K11" t="n">
-        <v>1.3971</v>
+        <v>0.5329</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6269</v>
+        <v>-0.1471</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.9487</v>
+        <v>-2.9102</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9883</v>
+        <v>-1.6828</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9604</v>
+        <v>-1.2274</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.1231</v>
+        <v>0.386</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.8951</v>
+        <v>-0.965</v>
       </c>
       <c r="R11" t="n">
-        <v>0.772</v>
+        <v>1.3511</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7628</v>
+        <v>0.0916</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2062</v>
+        <v>0.0017</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5565</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.228</v>
+        <v>-1.4079</v>
       </c>
       <c r="W11" t="n">
-        <v>1.5138</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.7418</v>
+        <v>-1.4079</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R. SANCHEZ SANCHEZ</t>
+          <t>J. SAEZ PEREZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.3698</v>
+        <v>-3.7132</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.2785</v>
+        <v>-0.4049</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.0913</v>
+        <v>-3.3084</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.5243</v>
+        <v>-1.1785</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.1498</v>
+        <v>0.4088</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.3745</v>
+        <v>-1.5873</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3859</v>
+        <v>0.7702</v>
       </c>
       <c r="K12" t="n">
-        <v>0.5329</v>
+        <v>1.3971</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.1471</v>
+        <v>-0.6269</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.9102</v>
+        <v>-1.9487</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.6828</v>
+        <v>-0.9883</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.2274</v>
+        <v>-0.9604</v>
       </c>
       <c r="P12" t="n">
-        <v>0.386</v>
+        <v>-2.1231</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.965</v>
+        <v>-2.8951</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3511</v>
+        <v>0.772</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8236</v>
+        <v>0.8163</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6993</v>
+        <v>0.2062</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1243</v>
+        <v>0.6101</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.4079</v>
+        <v>-1.228</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.5138</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.4079</v>
+        <v>-2.7418</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.7134</v>
+        <v>-6.0263</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.703</v>
+        <v>-4.0427</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.0104</v>
+        <v>-1.9836</v>
       </c>
       <c r="G13" t="n">
         <v>-6.0608</v>
@@ -1468,13 +1468,13 @@
         <v>0.965</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4726</v>
+        <v>0.2145</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5803</v>
+        <v>0.08</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1077</v>
+        <v>0.1345</v>
       </c>
       <c r="V13" t="n">
         <v>-0.18</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-21.5818</v>
+        <v>-21.2843</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.692499999999999</v>
+        <v>-0.3950999999999989</v>
       </c>
       <c r="F14" t="n">
-        <v>-20.889</v>
+        <v>-20.8893</v>
       </c>
       <c r="G14" t="n">
         <v>-12.6145</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.8684</v>
+        <v>-1.868399999999999</v>
       </c>
       <c r="I14" t="n">
         <v>-10.7461</v>
@@ -1546,10 +1546,10 @@
         <v>13.5105</v>
       </c>
       <c r="S14" t="n">
-        <v>6.4514</v>
+        <v>6.748699999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>1.3884</v>
+        <v>1.6858</v>
       </c>
       <c r="U14" t="n">
         <v>5.0629</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C. RIVERA MOTA</t>
+          <t>G. TSULAIA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>10.3509</v>
+        <v>11.2632</v>
       </c>
       <c r="E15" t="n">
-        <v>7.7974</v>
+        <v>10.432</v>
       </c>
       <c r="F15" t="n">
-        <v>2.5535</v>
+        <v>0.8312</v>
       </c>
       <c r="G15" t="n">
-        <v>6.4418</v>
+        <v>4.9089</v>
       </c>
       <c r="H15" t="n">
-        <v>2.339</v>
+        <v>0.5962</v>
       </c>
       <c r="I15" t="n">
-        <v>4.1028</v>
+        <v>4.3127</v>
       </c>
       <c r="J15" t="n">
-        <v>8.4641</v>
+        <v>7.2582</v>
       </c>
       <c r="K15" t="n">
-        <v>4.5898</v>
+        <v>2.7735</v>
       </c>
       <c r="L15" t="n">
-        <v>3.8743</v>
+        <v>4.4848</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.0223</v>
+        <v>-2.3494</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.2508</v>
+        <v>-2.1773</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2285</v>
+        <v>-0.1721</v>
       </c>
       <c r="P15" t="n">
-        <v>0.386</v>
+        <v>1.3511</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.8951</v>
+        <v>-1.9301</v>
       </c>
       <c r="R15" t="n">
         <v>3.2811</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7747000000000001</v>
+        <v>-1.0943</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.4132</v>
+        <v>-0.9938</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6384</v>
+        <v>-0.1005</v>
       </c>
       <c r="V15" t="n">
-        <v>4.2979</v>
+        <v>6.0976</v>
       </c>
       <c r="W15" t="n">
-        <v>3.6417</v>
+        <v>6.0976</v>
       </c>
       <c r="X15" t="n">
-        <v>0.6562</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. TSULAIA</t>
+          <t>C. RIVERA MOTA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>10.2675</v>
+        <v>10.463</v>
       </c>
       <c r="E16" t="n">
-        <v>10.1316</v>
+        <v>8.097899999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1359</v>
+        <v>2.3651</v>
       </c>
       <c r="G16" t="n">
-        <v>4.9089</v>
+        <v>6.4418</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5962</v>
+        <v>2.339</v>
       </c>
       <c r="I16" t="n">
-        <v>4.3127</v>
+        <v>4.1028</v>
       </c>
       <c r="J16" t="n">
-        <v>7.2582</v>
+        <v>8.4641</v>
       </c>
       <c r="K16" t="n">
-        <v>2.7735</v>
+        <v>4.5898</v>
       </c>
       <c r="L16" t="n">
-        <v>4.4848</v>
+        <v>3.8743</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.3494</v>
+        <v>-2.0223</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.1773</v>
+        <v>-2.2508</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1721</v>
+        <v>0.2285</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3511</v>
+        <v>0.386</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9301</v>
+        <v>-2.8951</v>
       </c>
       <c r="R16" t="n">
         <v>3.2811</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.09</v>
+        <v>-0.6627</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.2942</v>
+        <v>-1.1127</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7959000000000001</v>
+        <v>0.4501</v>
       </c>
       <c r="V16" t="n">
-        <v>6.0976</v>
+        <v>4.2979</v>
       </c>
       <c r="W16" t="n">
-        <v>6.0976</v>
+        <v>3.6417</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.6562</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.466</v>
+        <v>5.7995</v>
       </c>
       <c r="E17" t="n">
-        <v>3.8996</v>
+        <v>4.0998</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5664</v>
+        <v>1.6996</v>
       </c>
       <c r="G17" t="n">
         <v>2.1995</v>
@@ -1780,13 +1780,13 @@
         <v>3.0881</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.2896</v>
+        <v>-0.9560999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1752</v>
+        <v>-0.9749</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1144</v>
+        <v>0.0188</v>
       </c>
       <c r="V17" t="n">
         <v>3.398</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.977</v>
+        <v>1.2114</v>
       </c>
       <c r="E18" t="n">
-        <v>2.4626</v>
+        <v>2.1622</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.4855</v>
+        <v>-0.9508</v>
       </c>
       <c r="G18" t="n">
         <v>0.0585</v>
@@ -1858,13 +1858,13 @@
         <v>1.9301</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6835</v>
+        <v>-0.4491</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0912</v>
+        <v>-0.3916</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5923</v>
+        <v>-0.0575</v>
       </c>
       <c r="V18" t="n">
         <v>-0.3281</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1514</v>
+        <v>0.1781</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1514</v>
+        <v>0.1781</v>
       </c>
       <c r="G19" t="n">
         <v>0.1335</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3157</v>
+        <v>-0.2697</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8364</v>
+        <v>0.9365</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.152</v>
+        <v>-1.2062</v>
       </c>
       <c r="G20" t="n">
         <v>-1.6614</v>
@@ -2014,13 +2014,13 @@
         <v>1.7371</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3913</v>
+        <v>-0.3454</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6993</v>
+        <v>-0.5992</v>
       </c>
       <c r="U20" t="n">
-        <v>0.308</v>
+        <v>0.2538</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6908</v>
+        <v>-0.5038</v>
       </c>
       <c r="E21" t="n">
         <v>-0.7866</v>
       </c>
       <c r="F21" t="n">
-        <v>0.09569999999999999</v>
+        <v>0.2828</v>
       </c>
       <c r="G21" t="n">
         <v>-0.3405</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3503</v>
+        <v>-0.1633</v>
       </c>
       <c r="T21" t="n">
         <v>-0.119</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2313</v>
+        <v>-0.0443</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. CAMPBELL</t>
+          <t>D. MERKVILADZE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.9836</v>
+        <v>-2.0594</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7577</v>
+        <v>-1.5939</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.226</v>
+        <v>-0.4655</v>
       </c>
       <c r="G22" t="n">
-        <v>0.7619</v>
+        <v>0.1124</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8983</v>
+        <v>0.4037</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1364</v>
+        <v>-0.2913</v>
       </c>
       <c r="J22" t="n">
-        <v>1.8495</v>
+        <v>-0.0747</v>
       </c>
       <c r="K22" t="n">
-        <v>1.6867</v>
+        <v>0.4709</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1628</v>
+        <v>-0.5455</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.0876</v>
+        <v>0.1871</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7884</v>
+        <v>-0.06710000000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2992</v>
+        <v>0.2542</v>
       </c>
       <c r="P22" t="n">
-        <v>-4.0532</v>
+        <v>0.386</v>
       </c>
       <c r="Q22" t="n">
-        <v>-5.7902</v>
+        <v>-0.965</v>
       </c>
       <c r="R22" t="n">
-        <v>1.7371</v>
+        <v>1.3511</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4078</v>
+        <v>-0.7159</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3834</v>
+        <v>-0.5542</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0244</v>
+        <v>-0.1616</v>
       </c>
       <c r="V22" t="n">
-        <v>0.8999</v>
+        <v>-1.842</v>
       </c>
       <c r="W22" t="n">
-        <v>1.7997</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.8999</v>
+        <v>-1.842</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. MERKVILADZE</t>
+          <t>S. CAMPBELL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.641</v>
+        <v>-2.4979</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.6941</v>
+        <v>-2.4587</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.947</v>
+        <v>-0.0392</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1124</v>
+        <v>0.7619</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4037</v>
+        <v>0.8983</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2913</v>
+        <v>-0.1364</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.0747</v>
+        <v>1.8495</v>
       </c>
       <c r="K23" t="n">
-        <v>0.4709</v>
+        <v>1.6867</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5455</v>
+        <v>0.1628</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1871</v>
+        <v>-1.0876</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.06710000000000001</v>
+        <v>-0.7884</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2542</v>
+        <v>-0.2992</v>
       </c>
       <c r="P23" t="n">
-        <v>0.386</v>
+        <v>-4.0532</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.965</v>
+        <v>-5.7902</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3511</v>
+        <v>1.7371</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2975</v>
+        <v>-0.1064</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6544</v>
+        <v>-0.3176</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6432</v>
+        <v>0.2111</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.842</v>
+        <v>0.8999</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.7997</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.842</v>
+        <v>-0.8999</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>21.5817</v>
+        <v>23.5844</v>
       </c>
       <c r="E24" t="n">
-        <v>20.88920000000001</v>
+        <v>20.8892</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6923999999999998</v>
+        <v>2.6951</v>
       </c>
       <c r="G24" t="n">
         <v>12.6146</v>
@@ -2305,7 +2305,7 @@
         <v>13.1225</v>
       </c>
       <c r="L24" t="n">
-        <v>9.603699999999998</v>
+        <v>9.6037</v>
       </c>
       <c r="M24" t="n">
         <v>-10.1115</v>
@@ -2326,13 +2326,13 @@
         <v>16.4057</v>
       </c>
       <c r="S24" t="n">
-        <v>-6.4513</v>
+        <v>-4.4486</v>
       </c>
       <c r="T24" t="n">
-        <v>-5.063099999999999</v>
+        <v>-5.063</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.3885</v>
+        <v>0.6145</v>
       </c>
       <c r="V24" t="n">
         <v>12.5233</v>
